--- a/business_forms/040_innovation_contest_approval_form--business_forms.xlsx
+++ b/business_forms/040_innovation_contest_approval_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,36 +525,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>What is the category of the innovation?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Please provide a brief description of the innovation.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,81 +566,81 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>What is the assigned tool for the innovation?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Is this innovation a form?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>What is the Form ID?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Is this innovation a Business Forms type?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,64 +658,64 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>What is a description of the innovation?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>What tool would be used to implement this innovation?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>form_id_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Is this innovation approved?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,64 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What type of form is this innovation?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Form ID</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -799,10 +753,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
@@ -827,7 +781,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>form_id_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -844,7 +798,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>form_id_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -861,34 +815,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_id_choices</t>
+          <t>form_id_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_id_choices</t>
+          <t>form_id_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -929,7 +883,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -946,7 +900,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -963,34 +917,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_id_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_id_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>form_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Form 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>category_2_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>form_2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Form 2</t>
         </is>
       </c>
     </row>
